--- a/evaluation_forms/014_child_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/014_child_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,8 +939,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,12 +968,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'consistently_demonstrates',_'value':_'consistently'}</t>
+          <t>consistently_demonstrates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Consistently Demonstrates', 'value': 'consistently'}</t>
+          <t>Consistently Demonstrates</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'often_demonstrates',_'value':_'often'}</t>
+          <t>often_demonstrates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Often Demonstrates', 'value': 'often'}</t>
+          <t>Often Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_demonstrates',_'value':_'sometimes'}</t>
+          <t>sometimes_demonstrates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes Demonstrates', 'value': 'sometimes'}</t>
+          <t>Sometimes Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_demonstrates',_'value':_'rarely'}</t>
+          <t>rarely_demonstrates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely Demonstrates', 'value': 'rarely'}</t>
+          <t>Rarely Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'consistently_demonstrates',_'value':_'consistently'}</t>
+          <t>consistently_demonstrates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Consistently Demonstrates', 'value': 'consistently'}</t>
+          <t>Consistently Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'often_demonstrates',_'value':_'often'}</t>
+          <t>often_demonstrates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Often Demonstrates', 'value': 'often'}</t>
+          <t>Often Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_demonstrates',_'value':_'sometimes'}</t>
+          <t>sometimes_demonstrates</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes Demonstrates', 'value': 'sometimes'}</t>
+          <t>Sometimes Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_demonstrates',_'value':_'rarely'}</t>
+          <t>rarely_demonstrates</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely Demonstrates', 'value': 'rarely'}</t>
+          <t>Rarely Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'above_grade_level',_'value':_'above'}</t>
+          <t>above_grade_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Above Grade Level', 'value': 'above'}</t>
+          <t>Above Grade Level</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'at_grade_level',_'value':_'at'}</t>
+          <t>at_grade_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'At Grade Level', 'value': 'at'}</t>
+          <t>At Grade Level</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'below_grade_level',_'value':_'below'}</t>
+          <t>below_grade_level</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Below Grade Level', 'value': 'below'}</t>
+          <t>Below Grade Level</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'above_grade_level',_'value':_'above'}</t>
+          <t>above_grade_level</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Above Grade Level', 'value': 'above'}</t>
+          <t>Above Grade Level</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'at_grade_level',_'value':_'at'}</t>
+          <t>at_grade_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'At Grade Level', 'value': 'at'}</t>
+          <t>At Grade Level</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'below_grade_level',_'value':_'below'}</t>
+          <t>below_grade_level</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Below Grade Level', 'value': 'below'}</t>
+          <t>Below Grade Level</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'consistently_demonstrates',_'value':_'consistently'}</t>
+          <t>consistently_demonstrates</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Consistently Demonstrates', 'value': 'consistently'}</t>
+          <t>Consistently Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'often_demonstrates',_'value':_'often'}</t>
+          <t>often_demonstrates</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Often Demonstrates', 'value': 'often'}</t>
+          <t>Often Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_demonstrates',_'value':_'sometimes'}</t>
+          <t>sometimes_demonstrates</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes Demonstrates', 'value': 'sometimes'}</t>
+          <t>Sometimes Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_demonstrates',_'value':_'rarely'}</t>
+          <t>rarely_demonstrates</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely Demonstrates', 'value': 'rarely'}</t>
+          <t>Rarely Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'consistently_demonstrates',_'value':_'consistently'}</t>
+          <t>consistently_demonstrates</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Consistently Demonstrates', 'value': 'consistently'}</t>
+          <t>Consistently Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'often_demonstrates',_'value':_'often'}</t>
+          <t>often_demonstrates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Often Demonstrates', 'value': 'often'}</t>
+          <t>Often Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_demonstrates',_'value':_'sometimes'}</t>
+          <t>sometimes_demonstrates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes Demonstrates', 'value': 'sometimes'}</t>
+          <t>Sometimes Demonstrates</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_demonstrates',_'value':_'rarely'}</t>
+          <t>rarely_demonstrates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely Demonstrates', 'value': 'rarely'}</t>
+          <t>Rarely Demonstrates</t>
         </is>
       </c>
     </row>
